--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.46710562129792</v>
+        <v>11.77590466346091</v>
       </c>
       <c r="D2" t="n">
-        <v>72.19225291855888</v>
+        <v>11.73124109926582</v>
       </c>
       <c r="E2" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F2" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.8277615013973</v>
+        <v>9.722011243977063</v>
       </c>
       <c r="D3" t="n">
-        <v>58.73873267807754</v>
+        <v>9.5450440601876</v>
       </c>
       <c r="E3" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F3" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.06616088566492</v>
+        <v>7.48575114392055</v>
       </c>
       <c r="D4" t="n">
-        <v>45.07135820338256</v>
+        <v>7.324095708049666</v>
       </c>
       <c r="E4" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F4" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.04488627025963</v>
+        <v>9.269794018917191</v>
       </c>
       <c r="D5" t="n">
-        <v>55.92904687788389</v>
+        <v>9.088470117656133</v>
       </c>
       <c r="E5" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F5" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.37486137683076</v>
+        <v>6.885914973734998</v>
       </c>
       <c r="D6" t="n">
-        <v>42.09499251711281</v>
+        <v>6.840436284030831</v>
       </c>
       <c r="E6" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F6" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.34804932376858</v>
+        <v>7.369058015112396</v>
       </c>
       <c r="D7" t="n">
-        <v>45.59356304238644</v>
+        <v>7.408953994387796</v>
       </c>
       <c r="E7" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F7" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.4788641370744</v>
+        <v>2.19031542227459</v>
       </c>
       <c r="D8" t="n">
-        <v>12.37412661123885</v>
+        <v>2.010795574326314</v>
       </c>
       <c r="E8" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F8" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.86930278999623</v>
+        <v>6.153761703374388</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16156152240048</v>
+        <v>6.038753747390078</v>
       </c>
       <c r="E9" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F9" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.44637837063428</v>
+        <v>2.67253648522807</v>
       </c>
       <c r="D10" t="n">
-        <v>15.73241485837345</v>
+        <v>2.556517414485686</v>
       </c>
       <c r="E10" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F10" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.61763229586121</v>
+        <v>4.650365248077446</v>
       </c>
       <c r="D11" t="n">
-        <v>28.29049749088049</v>
+        <v>4.59720584226808</v>
       </c>
       <c r="E11" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F11" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.8576650975578</v>
+        <v>1.764370578353142</v>
       </c>
       <c r="D12" t="n">
-        <v>11.53413161724303</v>
+        <v>1.874296387801992</v>
       </c>
       <c r="E12" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F12" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.31986558236233</v>
+        <v>4.276978157133879</v>
       </c>
       <c r="D13" t="n">
-        <v>26.93073392769151</v>
+        <v>4.376244263249871</v>
       </c>
       <c r="E13" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F13" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.53008897262316</v>
+        <v>8.536139458051265</v>
       </c>
       <c r="D14" t="n">
-        <v>52.53668648031605</v>
+        <v>8.537211553051359</v>
       </c>
       <c r="E14" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F14" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.19186144664619</v>
+        <v>4.256177485080006</v>
       </c>
       <c r="D15" t="n">
-        <v>26.99832589125527</v>
+        <v>4.387227957328981</v>
       </c>
       <c r="E15" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F15" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.1425131429826</v>
+        <v>7.498158385734673</v>
       </c>
       <c r="D16" t="n">
-        <v>47.23508695044723</v>
+        <v>7.675701629447675</v>
       </c>
       <c r="E16" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F16" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.03988131140143</v>
+        <v>6.018980713102732</v>
       </c>
       <c r="D17" t="n">
-        <v>37.03864830623019</v>
+        <v>6.018780349762407</v>
       </c>
       <c r="E17" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F17" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>51.3557399616091</v>
+        <v>8.345307743761479</v>
       </c>
       <c r="D18" t="n">
-        <v>51.89775128319643</v>
+        <v>8.43338458351942</v>
       </c>
       <c r="E18" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F18" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>64.32131600170305</v>
+        <v>10.45221385027675</v>
       </c>
       <c r="D19" t="n">
-        <v>65.4371593293365</v>
+        <v>10.63353839101718</v>
       </c>
       <c r="E19" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F19" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.16862489514546</v>
+        <v>3.114901545461137</v>
       </c>
       <c r="D20" t="n">
-        <v>20.01025829758922</v>
+        <v>3.251666973358248</v>
       </c>
       <c r="E20" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F20" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>59.42213389794895</v>
+        <v>9.656096758416703</v>
       </c>
       <c r="D21" t="n">
-        <v>58.68850243221568</v>
+        <v>9.536881645235049</v>
       </c>
       <c r="E21" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F21" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>25.68717804204407</v>
+        <v>4.174166431832162</v>
       </c>
       <c r="D22" t="n">
-        <v>26.06036764057752</v>
+        <v>4.234809741593847</v>
       </c>
       <c r="E22" t="n">
-        <v>17.41380222268397</v>
+        <v>2.829742861186144</v>
       </c>
       <c r="F22" t="n">
-        <v>17.32024241045315</v>
+        <v>2.814539391698637</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
